--- a/task127/golden/d2a_package_split_winter_2026-27.xlsx
+++ b/task127/golden/d2a_package_split_winter_2026-27.xlsx
@@ -72,7 +72,7 @@
     <t>Hospitals with no packages: Ashby Vale Hospital.</t>
   </si>
   <si>
-    <t>Ashby Vale Hospital's covered patients would have left 3.60 nights sooner each with a package, the fewest of the five: most of them were also waiting for community equipment, and a package does not bring that forward.</t>
+    <t>Ashby Vale Hospital's covered patients would have left 3.14 nights sooner each with a package, the fewest of the five: most of them were also waiting for community equipment, and a package does not bring that forward.</t>
   </si>
   <si>
     <t>Covered patients exclude patients registered with Severnside practices and patients whose existing package restarted on discharge (allocation note SF-2026-14, section 3).</t>
@@ -634,13 +634,13 @@
         <v>508</v>
       </c>
       <c r="D5" s="5">
-        <v>6.647637795275591</v>
+        <v>6.391732283464567</v>
       </c>
       <c r="E5" s="4">
         <v>508</v>
       </c>
       <c r="F5" s="4">
-        <v>3377</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="6">
@@ -654,13 +654,13 @@
         <v>350</v>
       </c>
       <c r="D6" s="5">
-        <v>6.24</v>
+        <v>5.82</v>
       </c>
       <c r="E6" s="4">
         <v>350</v>
       </c>
       <c r="F6" s="4">
-        <v>2184</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="7">
@@ -674,13 +674,13 @@
         <v>120</v>
       </c>
       <c r="D7" s="5">
-        <v>5.258333333333334</v>
+        <v>5.35</v>
       </c>
       <c r="E7" s="4">
         <v>120</v>
       </c>
       <c r="F7" s="4">
-        <v>631</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -694,13 +694,13 @@
         <v>285</v>
       </c>
       <c r="D8" s="5">
-        <v>4.36140350877193</v>
+        <v>4.007017543859649</v>
       </c>
       <c r="E8" s="4">
         <v>222</v>
       </c>
       <c r="F8" s="4">
-        <v>968</v>
+        <v>890</v>
       </c>
     </row>
     <row r="9">
@@ -714,7 +714,7 @@
         <v>361</v>
       </c>
       <c r="D9" s="5">
-        <v>3.598337950138504</v>
+        <v>3.141274238227147</v>
       </c>
       <c r="E9" s="4">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>1200</v>
       </c>
       <c r="F10" s="7">
-        <v>7160</v>
+        <v>6816</v>
       </c>
     </row>
     <row r="12">
@@ -823,22 +823,22 @@
         <v>29</v>
       </c>
       <c r="B5" s="4">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C5" s="4">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="D5" s="4">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="E5" s="4">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="F5" s="4">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="G5" s="4">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
@@ -846,22 +846,22 @@
         <v>30</v>
       </c>
       <c r="B6" s="4">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C6" s="4">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D6" s="4">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E6" s="4">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F6" s="4">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="G6" s="4">
-        <v>204</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -869,22 +869,22 @@
         <v>31</v>
       </c>
       <c r="B7" s="4">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D7" s="4">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E7" s="4">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F7" s="4">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="G7" s="4">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
